--- a/courseware/Labs/Lab-03-DMAIC/Worked-Reference.xlsx
+++ b/courseware/Labs/Lab-03-DMAIC/Worked-Reference.xlsx
@@ -25491,7 +25491,7 @@
     <t xml:space="preserve">Plot and interpret</t>
   </si>
   <si>
-    <t xml:space="preserve">Create an Excel line chart of delivery_L_h by timestamp for baseline, monitoring and pilot, with the fixed baseline mean/UCL/LCL. Flag points outside the limits without refitting them. Report phase counts and affected IDs. Explain the monitoring shift as a signal requiring investigation, not a proven restriction diagnosis. Keep invalid and missing tests visible in QualityAudit.</t>
+    <t xml:space="preserve">Review the existing Analysis and SPC_Summary chart. Keep the prepared formulas and fixed baseline limits unchanged. Identify valid monitoring points outside the limits and check one example against the source row. Return only three sentences: observed signal, supporting evidence, and an unresolved limitation. Do not rebuild the chart or calculate capability.</t>
   </si>
   <si>
     <t xml:space="preserve">SPC4</t>
@@ -25518,7 +25518,7 @@
     <t xml:space="preserve">Calculate and prioritise</t>
   </si>
   <si>
-    <t xml:space="preserve">Add an Excel formula RPN=S*O*D for every row. Sort a view by RPN descending while preserving mode IDs and source rows. Add a separate high-severity review flag for S&gt;=9. Create an RPN column chart. Do not treat rank or low RPN as evidence of safety acceptance.</t>
+    <t xml:space="preserve">Review the prepared FMEA_Review. Check the RPN formulas for FM01 and FM04, preserving mode IDs and provisional scores. Explain why the severity-9 row still needs review. Return one evidence gap and one proposed action for FM01; keep residual ratings unassessed. Do not rebuild the table or chart.</t>
   </si>
   <si>
     <t xml:space="preserve">FMEA3</t>
@@ -25536,7 +25536,7 @@
     <t xml:space="preserve">Define and measure</t>
   </si>
   <si>
-    <t xml:space="preserve">Use WeeklyEvents, DefectCounts and Evidence. Draft a DMAIC table in Excel: phase, claim, metric, source, limitation, next action. Define the CTQ as delivery-test acceptance deviation, not chemical compliance. Calculate baseline and pilot rates using summed deviations divided by summed opportunities, not a simple average when denominators differ.</t>
+    <t xml:space="preserve">Review the prepared Rate_Comparison, WeeklyEvents and DMAIC tables. Check baseline and pilot rates using summed deviations divided by summed opportunities. Return three cells: measured change, limitation and next evidence. Do not create a full report or a new chart, and do not claim a causal effect from the short pilot.</t>
   </si>
   <si>
     <t xml:space="preserve">DMAIC2</t>

--- a/courseware/Labs/Lab-03-DMAIC/Worked-Reference.xlsx
+++ b/courseware/Labs/Lab-03-DMAIC/Worked-Reference.xlsx
@@ -24228,7 +24228,7 @@
     <t xml:space="preserve">How to use</t>
   </si>
   <si>
-    <t xml:space="preserve">Save a working copy of Starter.xlsx to your approved OneDrive or SharePoint location. Open it in Excel with your work/school account and use the Copilot side pane. Select the named table before prompting. If Copilot cannot edit, request the formula and insert it manually; record the fallback. Confirm tenant entitlement and supported workbook format before class. Keep the local raw files unchanged.</t>
+    <t xml:space="preserve">For the class, save a working copy of Worked-Reference.xlsx to approved OneDrive or SharePoint storage. Starter.xlsx is optional after-class practice. Open it in Excel with your work/school account and use the Copilot side pane. Select the named table before prompting. If Copilot cannot edit, request the formula and insert it manually; record the fallback. Confirm tenant entitlement and supported workbook format before class. Keep the local raw files unchanged.</t>
   </si>
   <si>
     <t xml:space="preserve">Workbook prompts</t>

--- a/courseware/Labs/Lab-03-DMAIC/Worked-Reference.xlsx
+++ b/courseware/Labs/Lab-03-DMAIC/Worked-Reference.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
   <si>
     <t xml:space="preserve">Lab 3 - Use Copilot in Excel to create a DMAIC summary</t>
   </si>
@@ -131,6 +131,36 @@
   </si>
   <si>
     <t xml:space="preserve">Two formula-based rates and a concise DMAIC table that states the problem, evidence, proposed test, and monitoring rule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RISE prompt builder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What this part does</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R - Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Six Sigma project assistant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I - Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only WeeklyData; four Baseline and two Pilot weeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S - Steps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculate both rates; create five-row DMAIC summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E - Expectations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show formulas; separate facts from hypotheses; no causal claim</t>
   </si>
   <si>
     <t xml:space="preserve">Deviation_Rate</t>
@@ -180,7 +210,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,6 +278,21 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF087F8C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF142C3E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -303,12 +348,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -328,8 +377,20 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -632,85 +693,85 @@
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="105"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="105"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>18</v>
       </c>
     </row>
@@ -736,107 +797,107 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="6" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="6" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="6" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -859,40 +920,81 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="120"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="90"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="81.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+    <row r="3" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+    <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -914,124 +1016,124 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="70"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="D1" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="6" t="n">
         <f aca="false">SUMIF(Weekly_Data!$B$2:$B$7,A2,Weekly_Data!$C$2:$C$7)</f>
         <v>400</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="6" t="n">
         <f aca="false">SUMIF(Weekly_Data!$B$2:$B$7,A2,Weekly_Data!$D$2:$D$7)</f>
         <v>36</v>
       </c>
-      <c r="D2" s="7" t="n">
+      <c r="D2" s="11" t="n">
         <f aca="false">C2/B2</f>
         <v>0.09</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="6" t="n">
         <f aca="false">SUMIF(Weekly_Data!$B$2:$B$7,A3,Weekly_Data!$C$2:$C$7)</f>
         <v>200</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <f aca="false">SUMIF(Weekly_Data!$B$2:$B$7,A3,Weekly_Data!$D$2:$D$7)</f>
         <v>7</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="11" t="n">
         <f aca="false">C3/B3</f>
         <v>0.035</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B5" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
